--- a/artfynd/A 31060-2026 artfynd.xlsx
+++ b/artfynd/A 31060-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82808883</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340767</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119783618</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,6 +1170,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984668</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1275,6 +1300,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984676</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1396,8 +1426,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984055</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31060-2026 artfynd.xlsx
+++ b/artfynd/A 31060-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125984668</v>
+        <v>135867093</v>
       </c>
       <c r="B5" t="n">
-        <v>58817</v>
+        <v>56859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,58 +1050,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ormkärrsskogen, Sura sn, Vstm</t>
+          <t>Ormkärret, Surahammar, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557957</v>
+        <v>557878</v>
       </c>
       <c r="R5" t="n">
-        <v>6617694</v>
+        <v>6617676</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,27 +1117,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vid bäcken</t>
+          <t>Registrerad med autobox (384 kHz). Inspelningarna analyserades med BTO Acoustic Pipeline. Dvärgpipistrell registrerades vid upprepade tillfällen, med hög klassificeringssäkerhet.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,89 +1146,76 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125984668</t>
+          <t>https://artportalen.se/Sighting/135867093</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125984676</v>
+        <v>135866979</v>
       </c>
       <c r="B6" t="n">
-        <v>58815</v>
+        <v>56838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208250</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ormkärret, Sura sn, Vstm</t>
+          <t>Ormkärret, Surahammar, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557917</v>
+        <v>557878</v>
       </c>
       <c r="R6" t="n">
-        <v>6617684</v>
+        <v>6617676</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1260,22 +1239,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Registrerad med autobox (384 kHz). Inspelningarna analyserades med BTO Acoustic Pipeline. Nordfladdermus registrerades vid upprepade tillfällen under båda inventeringsnätterna, med hög klassificeringssäkerhet. Hög aktivitet noterades under kvällen den 11 augusti mellan kl. 21:49 och 23:09. Ett flertal sekvenser klassificerades som feeding buzz, vilket indikerar aktivt födosök vid lokalen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,80 +1268,84 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125984676</t>
+          <t>https://artportalen.se/Sighting/135866979</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125984055</v>
+        <v>135867016</v>
       </c>
       <c r="B7" t="n">
-        <v>106061</v>
+        <v>56861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221101</v>
+        <v>206002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ormkärret, Sur sn, Vstm</t>
+          <t>Ormkärret, Surahammar, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558006</v>
+        <v>557878</v>
       </c>
       <c r="R7" t="n">
-        <v>6617735</v>
+        <v>6617676</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1381,27 +1369,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:46</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Litet bestånd</t>
+          <t>Registrerad med autobox (384 kHz). Inspelningarna analyserades med BTO Acoustic Pipeline. Brunlångöra registrerades vid upprepade tillfällen under båda inventeringsnätterna, med hög klassificeringssäkerhet.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,23 +1398,417 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135867016</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125984668</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ormkärrsskogen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>557957</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6617694</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vid bäcken</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984668</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125984676</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ormkärret, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>557917</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6617684</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984676</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125984055</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106061</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ormkärret, Sur sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>558006</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6617735</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Litet bestånd</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125984055</t>
         </is>
@@ -1440,6 +1822,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31060-2026 artfynd.xlsx
+++ b/artfynd/A 31060-2026 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>135867093</v>
       </c>
       <c r="B5" t="n">
-        <v>56859</v>
+        <v>56861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>135866979</v>
       </c>
       <c r="B6" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>135867016</v>
       </c>
       <c r="B7" t="n">
-        <v>56861</v>
+        <v>56863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31060-2026 artfynd.xlsx
+++ b/artfynd/A 31060-2026 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>135867093</v>
       </c>
       <c r="B5" t="n">
-        <v>56861</v>
+        <v>56862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>135866979</v>
       </c>
       <c r="B6" t="n">
-        <v>56840</v>
+        <v>56841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>135867016</v>
       </c>
       <c r="B7" t="n">
-        <v>56863</v>
+        <v>56864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31060-2026 artfynd.xlsx
+++ b/artfynd/A 31060-2026 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>135867093</v>
       </c>
       <c r="B5" t="n">
-        <v>56862</v>
+        <v>56866</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>135866979</v>
       </c>
       <c r="B6" t="n">
-        <v>56841</v>
+        <v>56845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>135867016</v>
       </c>
       <c r="B7" t="n">
-        <v>56864</v>
+        <v>56868</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31060-2026 artfynd.xlsx
+++ b/artfynd/A 31060-2026 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>135867093</v>
       </c>
       <c r="B5" t="n">
-        <v>56866</v>
+        <v>56867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>135866979</v>
       </c>
       <c r="B6" t="n">
-        <v>56845</v>
+        <v>56846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>135867016</v>
       </c>
       <c r="B7" t="n">
-        <v>56868</v>
+        <v>56869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31060-2026 artfynd.xlsx
+++ b/artfynd/A 31060-2026 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>135867093</v>
       </c>
       <c r="B5" t="n">
-        <v>56867</v>
+        <v>56872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>135866979</v>
       </c>
       <c r="B6" t="n">
-        <v>56846</v>
+        <v>56851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>135867016</v>
       </c>
       <c r="B7" t="n">
-        <v>56869</v>
+        <v>56874</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31060-2026 artfynd.xlsx
+++ b/artfynd/A 31060-2026 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>135867093</v>
       </c>
       <c r="B5" t="n">
-        <v>56872</v>
+        <v>56885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>135866979</v>
       </c>
       <c r="B6" t="n">
-        <v>56851</v>
+        <v>56864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>135867016</v>
       </c>
       <c r="B7" t="n">
-        <v>56874</v>
+        <v>56887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
